--- a/diseases/d005/1990-1994.xlsx
+++ b/diseases/d005/1990-1994.xlsx
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14831,7 +14831,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16031,7 +16031,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -25099,7 +25099,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -27059,7 +27059,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27459,7 +27459,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27859,7 +27859,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28259,7 +28259,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29059,7 +29059,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29459,7 +29459,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29859,7 +29859,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30659,7 +30659,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31059,7 +31059,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -40127,7 +40127,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -42477,7 +42477,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -42877,7 +42877,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43277,7 +43277,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43677,7 +43677,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44077,7 +44077,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44477,7 +44477,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -44877,7 +44877,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45277,7 +45277,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45677,7 +45677,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -46077,7 +46077,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46477,7 +46477,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -55155,7 +55155,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -57505,7 +57505,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -57905,7 +57905,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -58305,7 +58305,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -58705,7 +58705,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -59105,7 +59105,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -59505,7 +59505,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -59905,7 +59905,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -60305,7 +60305,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -60705,7 +60705,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -61105,7 +61105,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -61505,7 +61505,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -70183,7 +70183,7 @@
       </c>
       <c r="AM353" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN353" t="b">
@@ -72533,7 +72533,7 @@
       </c>
       <c r="AM365" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN365" t="b">
@@ -72933,7 +72933,7 @@
       </c>
       <c r="AM367" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN367" t="b">
@@ -73333,7 +73333,7 @@
       </c>
       <c r="AM369" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN369" t="b">
@@ -73733,7 +73733,7 @@
       </c>
       <c r="AM371" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN371" t="b">
@@ -74133,7 +74133,7 @@
       </c>
       <c r="AM373" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN373" t="b">
@@ -74533,7 +74533,7 @@
       </c>
       <c r="AM375" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN375" t="b">
@@ -74933,7 +74933,7 @@
       </c>
       <c r="AM377" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN377" t="b">
@@ -75333,7 +75333,7 @@
       </c>
       <c r="AM379" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN379" t="b">
@@ -75733,7 +75733,7 @@
       </c>
       <c r="AM381" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN381" t="b">
@@ -76133,7 +76133,7 @@
       </c>
       <c r="AM383" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN383" t="b">
@@ -76533,7 +76533,7 @@
       </c>
       <c r="AM385" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN385" t="b">

--- a/diseases/d005/1990-1994.xlsx
+++ b/diseases/d005/1990-1994.xlsx
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14831,7 +14831,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16031,7 +16031,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -25099,7 +25099,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -27059,7 +27059,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27459,7 +27459,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27859,7 +27859,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28259,7 +28259,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29059,7 +29059,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29459,7 +29459,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29859,7 +29859,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30659,7 +30659,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31059,7 +31059,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -40127,7 +40127,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -42477,7 +42477,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -42877,7 +42877,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43277,7 +43277,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43677,7 +43677,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44077,7 +44077,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44477,7 +44477,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -44877,7 +44877,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45277,7 +45277,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45677,7 +45677,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -46077,7 +46077,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46477,7 +46477,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -55155,7 +55155,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -57505,7 +57505,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -57905,7 +57905,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -58305,7 +58305,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -58705,7 +58705,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -59105,7 +59105,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -59505,7 +59505,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -59905,7 +59905,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -60305,7 +60305,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -60705,7 +60705,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -61105,7 +61105,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -61505,7 +61505,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -70183,7 +70183,7 @@
       </c>
       <c r="AM353" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN353" t="b">
@@ -72533,7 +72533,7 @@
       </c>
       <c r="AM365" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN365" t="b">
@@ -72933,7 +72933,7 @@
       </c>
       <c r="AM367" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN367" t="b">
@@ -73333,7 +73333,7 @@
       </c>
       <c r="AM369" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN369" t="b">
@@ -73733,7 +73733,7 @@
       </c>
       <c r="AM371" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN371" t="b">
@@ -74133,7 +74133,7 @@
       </c>
       <c r="AM373" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN373" t="b">
@@ -74533,7 +74533,7 @@
       </c>
       <c r="AM375" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN375" t="b">
@@ -74933,7 +74933,7 @@
       </c>
       <c r="AM377" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN377" t="b">
@@ -75333,7 +75333,7 @@
       </c>
       <c r="AM379" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN379" t="b">
@@ -75733,7 +75733,7 @@
       </c>
       <c r="AM381" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN381" t="b">
@@ -76133,7 +76133,7 @@
       </c>
       <c r="AM383" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN383" t="b">
@@ -76533,7 +76533,7 @@
       </c>
       <c r="AM385" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN385" t="b">
